--- a/spec-tech/ig/StructureDefinition-xdm-actor-snr.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-actor-snr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-19T17:20:25+00:00</t>
+    <t>2026-07-21T08:40:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-actor-snr.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-actor-snr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:40:48+00:00</t>
+    <t>2026-07-21T15:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-actor-snr.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-actor-snr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T15:50:20+00:00</t>
+    <t>2026-07-21T16:28:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-actor-snr.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-actor-snr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:28:50+00:00</t>
+    <t>2026-07-21T16:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-actor-snr.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-actor-snr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:53:48+00:00</t>
+    <t>2026-07-22T08:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-actor-snr.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-actor-snr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T08:07:11+00:00</t>
+    <t>2026-07-22T10:39:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-actor-snr.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-actor-snr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:39:39+00:00</t>
+    <t>2026-07-22T17:16:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -332,7 +332,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve"> Autorité d’affectation</t>
+    <t>Autorité d’affectation</t>
   </si>
   <si>
     <t>xdm-actor-xds.XCN9</t>

--- a/spec-tech/ig/StructureDefinition-xdm-actor-snr.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-actor-snr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T17:16:50+00:00</t>
+    <t>2026-07-23T08:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
